--- a/docs/export-templates/AI问书_全域订阅订单数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域订阅订单数据导出.xlsx
@@ -169,6 +169,9 @@
     <t>李娜</t>
   </si>
   <si>
+    <t>已过期</t>
+  </si>
+  <si>
     <t>SUB202505201038-MED</t>
   </si>
   <si>
@@ -179,9 +182,6 @@
   </si>
   <si>
     <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>已过期</t>
   </si>
 </sst>
 </file>
@@ -874,12 +874,12 @@
         <v>51</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>17</v>
@@ -891,31 +891,31 @@
         <v>19</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
